--- a/사업자(상세)일괄등록_추가.xlsx
+++ b/사업자(상세)일괄등록_추가.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335B3289-1824-461E-8CF1-BF70487BC64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903085F9-9AEC-4196-895C-9CCFE182AA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="거래처" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="1180">
   <si>
     <t>업태</t>
   </si>
@@ -4012,6 +4012,285 @@
   </si>
   <si>
     <t>lejaeyoun@naver.com</t>
+  </si>
+  <si>
+    <t>587-85-02308</t>
+  </si>
+  <si>
+    <t>고혜진</t>
+  </si>
+  <si>
+    <t>stoutkhj@naver.com</t>
+  </si>
+  <si>
+    <t>306-03-22602</t>
+  </si>
+  <si>
+    <t>한관희</t>
+  </si>
+  <si>
+    <t>hkh8817@naver.com</t>
+  </si>
+  <si>
+    <t>416-09-29452</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>김채휴</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>leeyk4400@naver.com</t>
+  </si>
+  <si>
+    <t>505-81-51041</t>
+  </si>
+  <si>
+    <t>김칠석</t>
+  </si>
+  <si>
+    <t>503-81-99146</t>
+  </si>
+  <si>
+    <t>설우식</t>
+  </si>
+  <si>
+    <t>dams44123@hometax.go.kr</t>
+  </si>
+  <si>
+    <t>379-88-03139</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>437-88-02722</t>
+  </si>
+  <si>
+    <t>기민석</t>
+  </si>
+  <si>
+    <t>kidacom@naver.com</t>
+  </si>
+  <si>
+    <t>314-86-53701</t>
+  </si>
+  <si>
+    <t>서현식</t>
+  </si>
+  <si>
+    <t>khyun8815@daum.net</t>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>502-03-26657</t>
+  </si>
+  <si>
+    <t>남준철</t>
+  </si>
+  <si>
+    <t>214477@hanmail.net</t>
+  </si>
+  <si>
+    <t>303-10-87695</t>
+  </si>
+  <si>
+    <t>고두환</t>
+  </si>
+  <si>
+    <t>Loding@naver.com</t>
+  </si>
+  <si>
+    <t>487-18-00463</t>
+  </si>
+  <si>
+    <t>정기용</t>
+  </si>
+  <si>
+    <t>sieun4681@naver.com</t>
+  </si>
+  <si>
+    <t>252-86-02898</t>
+  </si>
+  <si>
+    <t>남귀우</t>
+  </si>
+  <si>
+    <t>kwinamand@naver.com</t>
+  </si>
+  <si>
+    <t>119-73-00045</t>
+  </si>
+  <si>
+    <t>홍영동</t>
+  </si>
+  <si>
+    <t>sun620462@naver.com</t>
+  </si>
+  <si>
+    <t>302-01-83388</t>
+  </si>
+  <si>
+    <t>박규서</t>
+  </si>
+  <si>
+    <t>PKS8338@hometax.go.kr</t>
+  </si>
+  <si>
+    <t>575-05-01551</t>
+  </si>
+  <si>
+    <t>박진호</t>
+  </si>
+  <si>
+    <t>club2355@naver.com</t>
+  </si>
+  <si>
+    <t>443-76-00139</t>
+  </si>
+  <si>
+    <t>이돈기</t>
+  </si>
+  <si>
+    <t>KMMS2017@naver.com</t>
+  </si>
+  <si>
+    <t>128-27-57166</t>
+  </si>
+  <si>
+    <t>백순희</t>
+  </si>
+  <si>
+    <t>410-17-34118</t>
+  </si>
+  <si>
+    <t>조복태</t>
+  </si>
+  <si>
+    <t>proauto1@naver.com</t>
+  </si>
+  <si>
+    <t>324-37-00464</t>
+  </si>
+  <si>
+    <t>배용섭</t>
+  </si>
+  <si>
+    <t>Raid617@gmail.com</t>
+  </si>
+  <si>
+    <t>513-16-70662</t>
+  </si>
+  <si>
+    <t>이동혁</t>
+  </si>
+  <si>
+    <t>dongpali1978@hanmail.net</t>
+  </si>
+  <si>
+    <t>305-33-82109</t>
+  </si>
+  <si>
+    <t>황혜숙</t>
+  </si>
+  <si>
+    <t>rhwogy@naver.com</t>
+  </si>
+  <si>
+    <t>122-01-63748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강동수 외1 </t>
+  </si>
+  <si>
+    <t>VOLIM77@hometax.go.kr</t>
+  </si>
+  <si>
+    <t>552-86-02615</t>
+  </si>
+  <si>
+    <t>서정우</t>
+  </si>
+  <si>
+    <t>gksrnr0767@naver.com</t>
+  </si>
+  <si>
+    <t>138-01-48780</t>
+  </si>
+  <si>
+    <t>박현중</t>
+  </si>
+  <si>
+    <t>AUTO4040@naver.com</t>
+  </si>
+  <si>
+    <t>610-40-15252</t>
+  </si>
+  <si>
+    <t>최성재</t>
+  </si>
+  <si>
+    <t>koreaauto33@hometax.go.kr</t>
+  </si>
+  <si>
+    <t>514-07-99049</t>
+  </si>
+  <si>
+    <t>강락원</t>
+  </si>
+  <si>
+    <t>nwkang007@hanmail.com</t>
+  </si>
+  <si>
+    <t>503-21-16291</t>
+  </si>
+  <si>
+    <t>김진태</t>
+  </si>
+  <si>
+    <t>215-03-36659</t>
+  </si>
+  <si>
+    <t>조흥연</t>
+  </si>
+  <si>
+    <t>gkstls3253@hanmail.net</t>
+  </si>
+  <si>
+    <t>111-02-01171</t>
+  </si>
+  <si>
+    <t>이주연</t>
+  </si>
+  <si>
+    <t>2CAT@naver.com</t>
+  </si>
+  <si>
+    <t>262-02-00432</t>
+  </si>
+  <si>
+    <t>박영효</t>
+  </si>
+  <si>
+    <t>411-08-87601</t>
+  </si>
+  <si>
+    <t>정종삼</t>
+  </si>
+  <si>
+    <t>kiss1367@nate.com</t>
+  </si>
+  <si>
+    <t>410-27-15314</t>
+  </si>
+  <si>
+    <t>김원규</t>
+  </si>
+  <si>
+    <t>you3022@naver.com</t>
   </si>
 </sst>
 </file>
@@ -4693,18 +4972,18 @@
   <dimension ref="A1:T233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="2" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="55.625" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="13.875" style="3" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="8" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.375" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="55.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="9.625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.75" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="11.375" style="1" bestFit="1" customWidth="1"/>
@@ -4778,11 +5057,15 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
+      <c r="A2" s="23" t="s">
+        <v>1094</v>
+      </c>
       <c r="B2" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="24" t="s">
+        <v>1095</v>
+      </c>
       <c r="D2" s="13"/>
       <c r="E2" s="14" t="s">
         <v>359</v>
@@ -4798,7 +5081,9 @@
       <c r="J2" s="15"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="M2" s="22" t="s">
+        <v>1096</v>
+      </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
       <c r="P2" s="13"/>
@@ -5468,11 +5753,15 @@
       <c r="T21" s="15"/>
     </row>
     <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="22" t="s">
+        <v>1099</v>
+      </c>
       <c r="B22" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="13"/>
+      <c r="C22" s="22" t="s">
+        <v>1100</v>
+      </c>
       <c r="D22" s="13"/>
       <c r="E22" s="14" t="s">
         <v>378</v>
@@ -5488,7 +5777,9 @@
       <c r="J22" s="15"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="M22" s="22" t="s">
+        <v>1101</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13"/>
       <c r="P22" s="13"/>
@@ -6096,11 +6387,15 @@
       <c r="T39" s="15"/>
     </row>
     <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
+      <c r="A40" s="22" t="s">
+        <v>1104</v>
+      </c>
       <c r="B40" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C40" s="13"/>
+      <c r="C40" s="22" t="s">
+        <v>1105</v>
+      </c>
       <c r="D40" s="13"/>
       <c r="E40" s="14" t="s">
         <v>396</v>
@@ -6116,7 +6411,9 @@
       <c r="J40" s="15"/>
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
+      <c r="M40" s="22" t="s">
+        <v>1106</v>
+      </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -7458,11 +7755,15 @@
       <c r="T79" s="15"/>
     </row>
     <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="14"/>
+      <c r="A80" s="22" t="s">
+        <v>1114</v>
+      </c>
       <c r="B80" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="C80" s="13"/>
+      <c r="C80" s="22" t="s">
+        <v>1115</v>
+      </c>
       <c r="D80" s="13"/>
       <c r="E80" s="14" t="s">
         <v>436</v>
@@ -7478,7 +7779,9 @@
       <c r="J80" s="15"/>
       <c r="K80" s="13"/>
       <c r="L80" s="13"/>
-      <c r="M80" s="13"/>
+      <c r="M80" s="22" t="s">
+        <v>1116</v>
+      </c>
       <c r="N80" s="13"/>
       <c r="O80" s="13"/>
       <c r="P80" s="13"/>
@@ -7586,11 +7889,15 @@
       <c r="T83" s="15"/>
     </row>
     <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
+      <c r="A84" s="22" t="s">
+        <v>1117</v>
+      </c>
       <c r="B84" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C84" s="13"/>
+      <c r="C84" s="22" t="s">
+        <v>1118</v>
+      </c>
       <c r="D84" s="13"/>
       <c r="E84" s="14" t="s">
         <v>440</v>
@@ -7606,7 +7913,9 @@
       <c r="J84" s="15"/>
       <c r="K84" s="13"/>
       <c r="L84" s="13"/>
-      <c r="M84" s="13"/>
+      <c r="M84" s="22" t="s">
+        <v>1119</v>
+      </c>
       <c r="N84" s="13"/>
       <c r="O84" s="13"/>
       <c r="P84" s="13"/>
@@ -7650,11 +7959,15 @@
       <c r="T85" s="15"/>
     </row>
     <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="13"/>
+      <c r="A86" s="22" t="s">
+        <v>1120</v>
+      </c>
       <c r="B86" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="C86" s="13"/>
+      <c r="C86" s="22" t="s">
+        <v>1121</v>
+      </c>
       <c r="D86" s="13"/>
       <c r="E86" s="14" t="s">
         <v>442</v>
@@ -7670,7 +7983,9 @@
       <c r="J86" s="15"/>
       <c r="K86" s="13"/>
       <c r="L86" s="13"/>
-      <c r="M86" s="13"/>
+      <c r="M86" s="22" t="s">
+        <v>1122</v>
+      </c>
       <c r="N86" s="13"/>
       <c r="O86" s="13"/>
       <c r="P86" s="13"/>
@@ -7682,11 +7997,15 @@
       <c r="T86" s="15"/>
     </row>
     <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
+      <c r="A87" s="22" t="s">
+        <v>1129</v>
+      </c>
       <c r="B87" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="13"/>
+      <c r="C87" s="22" t="s">
+        <v>1130</v>
+      </c>
       <c r="D87" s="13"/>
       <c r="E87" s="14" t="s">
         <v>443</v>
@@ -7702,7 +8021,9 @@
       <c r="J87" s="15"/>
       <c r="K87" s="13"/>
       <c r="L87" s="13"/>
-      <c r="M87" s="13"/>
+      <c r="M87" s="22" t="s">
+        <v>1131</v>
+      </c>
       <c r="N87" s="13"/>
       <c r="O87" s="13"/>
       <c r="P87" s="13"/>
@@ -7778,11 +8099,15 @@
       <c r="T89" s="15"/>
     </row>
     <row r="90" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="14"/>
+      <c r="A90" s="22" t="s">
+        <v>1135</v>
+      </c>
       <c r="B90" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C90" s="13"/>
+      <c r="C90" s="22" t="s">
+        <v>1136</v>
+      </c>
       <c r="D90" s="13"/>
       <c r="E90" s="14" t="s">
         <v>446</v>
@@ -7798,7 +8123,9 @@
       <c r="J90" s="15"/>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
-      <c r="M90" s="13"/>
+      <c r="M90" s="22" t="s">
+        <v>1137</v>
+      </c>
       <c r="N90" s="13"/>
       <c r="O90" s="13"/>
       <c r="P90" s="13"/>
@@ -7842,11 +8169,15 @@
       <c r="T91" s="15"/>
     </row>
     <row r="92" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="13"/>
+      <c r="A92" s="22" t="s">
+        <v>1137</v>
+      </c>
       <c r="B92" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C92" s="13"/>
+      <c r="C92" s="22" t="s">
+        <v>1138</v>
+      </c>
       <c r="D92" s="13"/>
       <c r="E92" s="14" t="s">
         <v>448</v>
@@ -7862,7 +8193,9 @@
       <c r="J92" s="15"/>
       <c r="K92" s="13"/>
       <c r="L92" s="13"/>
-      <c r="M92" s="13"/>
+      <c r="M92" s="22" t="s">
+        <v>1139</v>
+      </c>
       <c r="N92" s="13"/>
       <c r="O92" s="13"/>
       <c r="P92" s="13"/>
@@ -7906,11 +8239,15 @@
       <c r="T93" s="15"/>
     </row>
     <row r="94" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="13"/>
+      <c r="A94" s="22" t="s">
+        <v>1126</v>
+      </c>
       <c r="B94" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C94" s="13"/>
+      <c r="C94" s="22" t="s">
+        <v>1127</v>
+      </c>
       <c r="D94" s="13"/>
       <c r="E94" s="14" t="s">
         <v>450</v>
@@ -7926,7 +8263,9 @@
       <c r="J94" s="15"/>
       <c r="K94" s="13"/>
       <c r="L94" s="13"/>
-      <c r="M94" s="13"/>
+      <c r="M94" s="22" t="s">
+        <v>1128</v>
+      </c>
       <c r="N94" s="13"/>
       <c r="O94" s="13"/>
       <c r="P94" s="13"/>
@@ -7938,11 +8277,15 @@
       <c r="T94" s="15"/>
     </row>
     <row r="95" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="14"/>
+      <c r="A95" s="23" t="s">
+        <v>981</v>
+      </c>
       <c r="B95" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C95" s="13"/>
+      <c r="C95" s="22" t="s">
+        <v>986</v>
+      </c>
       <c r="D95" s="13"/>
       <c r="E95" s="14" t="s">
         <v>451</v>
@@ -7958,7 +8301,9 @@
       <c r="J95" s="15"/>
       <c r="K95" s="13"/>
       <c r="L95" s="13"/>
-      <c r="M95" s="13"/>
+      <c r="M95" s="22" t="s">
+        <v>1006</v>
+      </c>
       <c r="N95" s="13"/>
       <c r="O95" s="13"/>
       <c r="P95" s="13"/>
@@ -7970,11 +8315,15 @@
       <c r="T95" s="15"/>
     </row>
     <row r="96" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="13"/>
+      <c r="A96" s="22" t="s">
+        <v>1143</v>
+      </c>
       <c r="B96" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="C96" s="13"/>
+      <c r="C96" s="22" t="s">
+        <v>1144</v>
+      </c>
       <c r="D96" s="13"/>
       <c r="E96" s="14" t="s">
         <v>452</v>
@@ -7990,7 +8339,9 @@
       <c r="J96" s="15"/>
       <c r="K96" s="13"/>
       <c r="L96" s="13"/>
-      <c r="M96" s="13"/>
+      <c r="M96" s="22" t="s">
+        <v>1145</v>
+      </c>
       <c r="N96" s="13"/>
       <c r="O96" s="13"/>
       <c r="P96" s="13"/>
@@ -8002,14 +8353,14 @@
       <c r="T96" s="15"/>
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="23" t="s">
-        <v>981</v>
+      <c r="A97" s="22" t="s">
+        <v>1177</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>223</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>986</v>
+        <v>1178</v>
       </c>
       <c r="D97" s="13"/>
       <c r="E97" s="14" t="s">
@@ -8027,7 +8378,7 @@
       <c r="K97" s="13"/>
       <c r="L97" s="13"/>
       <c r="M97" s="22" t="s">
-        <v>1006</v>
+        <v>1179</v>
       </c>
       <c r="N97" s="13"/>
       <c r="O97" s="13"/>
@@ -8040,11 +8391,15 @@
       <c r="T97" s="15"/>
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="14"/>
+      <c r="A98" s="22" t="s">
+        <v>1146</v>
+      </c>
       <c r="B98" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="C98" s="13"/>
+      <c r="C98" s="22" t="s">
+        <v>1147</v>
+      </c>
       <c r="D98" s="13"/>
       <c r="E98" s="14" t="s">
         <v>454</v>
@@ -8060,7 +8415,9 @@
       <c r="J98" s="15"/>
       <c r="K98" s="13"/>
       <c r="L98" s="13"/>
-      <c r="M98" s="13"/>
+      <c r="M98" s="22" t="s">
+        <v>1148</v>
+      </c>
       <c r="N98" s="13"/>
       <c r="O98" s="13"/>
       <c r="P98" s="13"/>
@@ -8072,11 +8429,15 @@
       <c r="T98" s="15"/>
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="14"/>
+      <c r="A99" s="22" t="s">
+        <v>1152</v>
+      </c>
       <c r="B99" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="C99" s="13"/>
+      <c r="C99" s="22" t="s">
+        <v>1153</v>
+      </c>
       <c r="D99" s="13"/>
       <c r="E99" s="14" t="s">
         <v>455</v>
@@ -8092,7 +8453,9 @@
       <c r="J99" s="15"/>
       <c r="K99" s="13"/>
       <c r="L99" s="13"/>
-      <c r="M99" s="13"/>
+      <c r="M99" s="22" t="s">
+        <v>1154</v>
+      </c>
       <c r="N99" s="13"/>
       <c r="O99" s="13"/>
       <c r="P99" s="13"/>
@@ -8104,11 +8467,15 @@
       <c r="T99" s="15"/>
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="13"/>
+      <c r="A100" s="22" t="s">
+        <v>1155</v>
+      </c>
       <c r="B100" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C100" s="13"/>
+      <c r="C100" s="22" t="s">
+        <v>1156</v>
+      </c>
       <c r="D100" s="13"/>
       <c r="E100" s="14" t="s">
         <v>456</v>
@@ -8124,7 +8491,9 @@
       <c r="J100" s="15"/>
       <c r="K100" s="13"/>
       <c r="L100" s="13"/>
-      <c r="M100" s="13"/>
+      <c r="M100" s="22" t="s">
+        <v>1157</v>
+      </c>
       <c r="N100" s="13"/>
       <c r="O100" s="13"/>
       <c r="P100" s="13"/>
@@ -8136,11 +8505,15 @@
       <c r="T100" s="15"/>
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="13"/>
+      <c r="A101" s="22" t="s">
+        <v>1149</v>
+      </c>
       <c r="B101" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="13"/>
+      <c r="C101" s="22" t="s">
+        <v>1150</v>
+      </c>
       <c r="D101" s="13"/>
       <c r="E101" s="14" t="s">
         <v>457</v>
@@ -8156,7 +8529,9 @@
       <c r="J101" s="15"/>
       <c r="K101" s="13"/>
       <c r="L101" s="13"/>
-      <c r="M101" s="13"/>
+      <c r="M101" s="22" t="s">
+        <v>1151</v>
+      </c>
       <c r="N101" s="13"/>
       <c r="O101" s="13"/>
       <c r="P101" s="13"/>
@@ -8168,11 +8543,15 @@
       <c r="T101" s="15"/>
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="13"/>
+      <c r="A102" s="22" t="s">
+        <v>1158</v>
+      </c>
       <c r="B102" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="13"/>
+      <c r="C102" s="22" t="s">
+        <v>1159</v>
+      </c>
       <c r="D102" s="13"/>
       <c r="E102" s="14" t="s">
         <v>458</v>
@@ -8188,7 +8567,9 @@
       <c r="J102" s="15"/>
       <c r="K102" s="13"/>
       <c r="L102" s="13"/>
-      <c r="M102" s="13"/>
+      <c r="M102" s="22" t="s">
+        <v>1160</v>
+      </c>
       <c r="N102" s="13"/>
       <c r="O102" s="13"/>
       <c r="P102" s="13"/>
@@ -8200,11 +8581,15 @@
       <c r="T102" s="15"/>
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="13"/>
+      <c r="A103" s="22" t="s">
+        <v>1161</v>
+      </c>
       <c r="B103" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C103" s="13"/>
+      <c r="C103" s="22" t="s">
+        <v>1162</v>
+      </c>
       <c r="D103" s="13"/>
       <c r="E103" s="14" t="s">
         <v>459</v>
@@ -8220,7 +8605,9 @@
       <c r="J103" s="15"/>
       <c r="K103" s="13"/>
       <c r="L103" s="13"/>
-      <c r="M103" s="13"/>
+      <c r="M103" s="22" t="s">
+        <v>1163</v>
+      </c>
       <c r="N103" s="13"/>
       <c r="O103" s="13"/>
       <c r="P103" s="13"/>
@@ -8232,11 +8619,15 @@
       <c r="T103" s="15"/>
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="13"/>
+      <c r="A104" s="22" t="s">
+        <v>1164</v>
+      </c>
       <c r="B104" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C104" s="13"/>
+      <c r="C104" s="22" t="s">
+        <v>1165</v>
+      </c>
       <c r="D104" s="13"/>
       <c r="E104" s="14" t="s">
         <v>460</v>
@@ -8264,11 +8655,15 @@
       <c r="T104" s="15"/>
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="13"/>
+      <c r="A105" s="22" t="s">
+        <v>1166</v>
+      </c>
       <c r="B105" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C105" s="13"/>
+      <c r="C105" s="22" t="s">
+        <v>1167</v>
+      </c>
       <c r="D105" s="13"/>
       <c r="E105" s="14" t="s">
         <v>461</v>
@@ -8284,7 +8679,9 @@
       <c r="J105" s="15"/>
       <c r="K105" s="13"/>
       <c r="L105" s="13"/>
-      <c r="M105" s="13"/>
+      <c r="M105" s="22" t="s">
+        <v>1168</v>
+      </c>
       <c r="N105" s="13"/>
       <c r="O105" s="13"/>
       <c r="P105" s="13"/>
@@ -8296,11 +8693,15 @@
       <c r="T105" s="15"/>
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="13"/>
+      <c r="A106" s="22" t="s">
+        <v>1169</v>
+      </c>
       <c r="B106" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C106" s="13"/>
+      <c r="C106" s="22" t="s">
+        <v>1170</v>
+      </c>
       <c r="D106" s="13"/>
       <c r="E106" s="14" t="s">
         <v>462</v>
@@ -8316,7 +8717,9 @@
       <c r="J106" s="15"/>
       <c r="K106" s="13"/>
       <c r="L106" s="13"/>
-      <c r="M106" s="13"/>
+      <c r="M106" s="22" t="s">
+        <v>1171</v>
+      </c>
       <c r="N106" s="13"/>
       <c r="O106" s="13"/>
       <c r="P106" s="13"/>
@@ -8616,11 +9019,15 @@
       <c r="T115" s="15"/>
     </row>
     <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="13"/>
+      <c r="A116" s="22" t="s">
+        <v>1140</v>
+      </c>
       <c r="B116" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="13"/>
+      <c r="C116" s="22" t="s">
+        <v>1141</v>
+      </c>
       <c r="D116" s="13"/>
       <c r="E116" s="14" t="s">
         <v>472</v>
@@ -8636,7 +9043,9 @@
       <c r="J116" s="15"/>
       <c r="K116" s="13"/>
       <c r="L116" s="13"/>
-      <c r="M116" s="13"/>
+      <c r="M116" s="22" t="s">
+        <v>1142</v>
+      </c>
       <c r="N116" s="13"/>
       <c r="O116" s="13"/>
       <c r="P116" s="13"/>
@@ -9214,11 +9623,15 @@
       <c r="T133" s="15"/>
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="13"/>
+      <c r="A134" s="22" t="s">
+        <v>1097</v>
+      </c>
       <c r="B134" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C134" s="13"/>
+      <c r="C134" s="22" t="s">
+        <v>1098</v>
+      </c>
       <c r="D134" s="13"/>
       <c r="E134" s="14" t="s">
         <v>490</v>
@@ -9572,11 +9985,15 @@
       <c r="T144" s="15"/>
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="13"/>
+      <c r="A145" s="22" t="s">
+        <v>1123</v>
+      </c>
       <c r="B145" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C145" s="13"/>
+      <c r="C145" s="22" t="s">
+        <v>1124</v>
+      </c>
       <c r="D145" s="13"/>
       <c r="E145" s="14" t="s">
         <v>501</v>
@@ -9592,7 +10009,9 @@
       <c r="J145" s="15"/>
       <c r="K145" s="13"/>
       <c r="L145" s="13"/>
-      <c r="M145" s="13"/>
+      <c r="M145" s="22" t="s">
+        <v>1125</v>
+      </c>
       <c r="N145" s="13"/>
       <c r="O145" s="13"/>
       <c r="P145" s="13"/>
@@ -9636,11 +10055,15 @@
       <c r="T146" s="15"/>
     </row>
     <row r="147" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="13"/>
+      <c r="A147" s="22" t="s">
+        <v>1102</v>
+      </c>
       <c r="B147" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="C147" s="13"/>
+      <c r="C147" s="22" t="s">
+        <v>1103</v>
+      </c>
       <c r="D147" s="13"/>
       <c r="E147" s="14" t="s">
         <v>503</v>
@@ -9700,11 +10123,15 @@
       <c r="T148" s="15"/>
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="13"/>
+      <c r="A149" s="22" t="s">
+        <v>1172</v>
+      </c>
       <c r="B149" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="C149" s="13"/>
+      <c r="C149" s="22" t="s">
+        <v>1173</v>
+      </c>
       <c r="D149" s="13"/>
       <c r="E149" s="14" t="s">
         <v>505</v>
@@ -9936,11 +10363,15 @@
       <c r="T155" s="15"/>
     </row>
     <row r="156" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="13"/>
+      <c r="A156" s="22" t="s">
+        <v>1091</v>
+      </c>
       <c r="B156" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C156" s="13"/>
+      <c r="C156" s="22" t="s">
+        <v>1092</v>
+      </c>
       <c r="D156" s="13"/>
       <c r="E156" s="14" t="s">
         <v>512</v>
@@ -9956,7 +10387,9 @@
       <c r="J156" s="15"/>
       <c r="K156" s="13"/>
       <c r="L156" s="13"/>
-      <c r="M156" s="13"/>
+      <c r="M156" s="22" t="s">
+        <v>1093</v>
+      </c>
       <c r="N156" s="13"/>
       <c r="O156" s="13"/>
       <c r="P156" s="13"/>
@@ -10102,11 +10535,15 @@
       <c r="T160" s="15"/>
     </row>
     <row r="161" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="14"/>
+      <c r="A161" s="22" t="s">
+        <v>1132</v>
+      </c>
       <c r="B161" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="C161" s="13"/>
+      <c r="C161" s="22" t="s">
+        <v>1133</v>
+      </c>
       <c r="D161" s="13"/>
       <c r="E161" s="14" t="s">
         <v>517</v>
@@ -10122,7 +10559,9 @@
       <c r="J161" s="15"/>
       <c r="K161" s="13"/>
       <c r="L161" s="13"/>
-      <c r="M161" s="13"/>
+      <c r="M161" s="22" t="s">
+        <v>1134</v>
+      </c>
       <c r="N161" s="13"/>
       <c r="O161" s="13"/>
       <c r="P161" s="13"/>
@@ -10990,11 +11429,15 @@
       <c r="T187" s="15"/>
     </row>
     <row r="188" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="14"/>
+      <c r="A188" s="22" t="s">
+        <v>1107</v>
+      </c>
       <c r="B188" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C188" s="13"/>
+      <c r="C188" s="22" t="s">
+        <v>1108</v>
+      </c>
       <c r="D188" s="13"/>
       <c r="E188" s="14" t="s">
         <v>543</v>
@@ -11010,9 +11453,13 @@
       <c r="J188" s="15"/>
       <c r="K188" s="13"/>
       <c r="L188" s="13"/>
-      <c r="M188" s="13"/>
+      <c r="M188" s="22" t="s">
+        <v>1109</v>
+      </c>
       <c r="N188" s="13"/>
-      <c r="O188" s="13"/>
+      <c r="O188" s="13" t="s">
+        <v>1110</v>
+      </c>
       <c r="P188" s="13"/>
       <c r="Q188" s="16"/>
       <c r="R188" s="14" t="s">
@@ -11380,11 +11827,15 @@
       <c r="T199" s="15"/>
     </row>
     <row r="200" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="14"/>
+      <c r="A200" s="22" t="s">
+        <v>1174</v>
+      </c>
       <c r="B200" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C200" s="13"/>
+      <c r="C200" s="22" t="s">
+        <v>1175</v>
+      </c>
       <c r="D200" s="13"/>
       <c r="E200" s="14" t="s">
         <v>555</v>
@@ -11400,7 +11851,9 @@
       <c r="J200" s="15"/>
       <c r="K200" s="13"/>
       <c r="L200" s="13"/>
-      <c r="M200" s="13"/>
+      <c r="M200" s="22" t="s">
+        <v>1176</v>
+      </c>
       <c r="N200" s="13"/>
       <c r="O200" s="13"/>
       <c r="P200" s="13"/>
@@ -11412,11 +11865,15 @@
       <c r="T200" s="15"/>
     </row>
     <row r="201" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="13"/>
+      <c r="A201" s="22" t="s">
+        <v>1111</v>
+      </c>
       <c r="B201" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C201" s="13"/>
+      <c r="C201" s="22" t="s">
+        <v>1112</v>
+      </c>
       <c r="D201" s="13"/>
       <c r="E201" s="14" t="s">
         <v>556</v>
@@ -11432,7 +11889,9 @@
       <c r="J201" s="15"/>
       <c r="K201" s="13"/>
       <c r="L201" s="13"/>
-      <c r="M201" s="13"/>
+      <c r="M201" s="22" t="s">
+        <v>1113</v>
+      </c>
       <c r="N201" s="13"/>
       <c r="O201" s="13"/>
       <c r="P201" s="13"/>
@@ -11968,11 +12427,15 @@
       <c r="T217" s="15"/>
     </row>
     <row r="218" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="14"/>
+      <c r="A218" s="22" t="s">
+        <v>1088</v>
+      </c>
       <c r="B218" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="C218" s="13"/>
+      <c r="C218" s="22" t="s">
+        <v>1089</v>
+      </c>
       <c r="D218" s="13"/>
       <c r="E218" s="14" t="s">
         <v>572</v>
@@ -11988,7 +12451,9 @@
       <c r="J218" s="15"/>
       <c r="K218" s="13"/>
       <c r="L218" s="13"/>
-      <c r="M218" s="13"/>
+      <c r="M218" s="22" t="s">
+        <v>1090</v>
+      </c>
       <c r="N218" s="13"/>
       <c r="O218" s="13"/>
       <c r="P218" s="13"/>
